--- a/output/archive/BrindlewytheData/Studies/2017/BW17_0167/Results/BW17_0167_hERG_RUN03.xlsx
+++ b/output/archive/BrindlewytheData/Studies/2017/BW17_0167/Results/BW17_0167_hERG_RUN03.xlsx
@@ -173,7 +173,7 @@
   <commentList>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
-        <t>Geometric mean of accepted cells; censored replicates excluded</t>
+        <t>Geometric mean of finite cell IC50s when they are the majority of accepted cells; otherwise &gt;30 µM (&gt;10 µM where precipitation limited the top concentration). n = accepted cells (finite).</t>
       </text>
     </comment>
   </commentList>
@@ -497,13 +497,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -520,6 +520,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -559,12 +560,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Study Director</t>
+          <t>Study lead</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Dr B. Rowcroft</t>
+          <t>Dr B. Rowcroft (Screening Operations Director)</t>
         </is>
       </c>
     </row>
@@ -622,10 +623,11 @@
         <v>16</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Study summary (benchmark)</t>
+          <t>Study summary</t>
         </is>
       </c>
     </row>
@@ -777,6 +779,7 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -784,28 +787,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H45"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="13.5" customWidth="1" min="3" max="3"/>
-    <col width="13.5" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="17.1" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18.8" customWidth="1" min="2" max="2"/>
+    <col width="18.8" customWidth="1" min="3" max="3"/>
+    <col width="18.8" customWidth="1" min="4" max="4"/>
+    <col width="19.85" customWidth="1" min="5" max="5"/>
+    <col width="21.95" customWidth="1" min="6" max="6"/>
+    <col width="18.8" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>hERG automated patch clamp: tail-current IC50, 6-point, top 30 µM</t>
-        </is>
-      </c>
-    </row>
+          <t>hERG automated patch clamp: tail-current IC50 per cell, 6-point, top 30 µM</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
@@ -814,22 +818,22 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 1 (µM)</t>
+          <t>IC50 cell 1 (µM)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 2 (µM)</t>
+          <t>IC50 cell 2 (µM)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>IC50 rep 3 (µM)</t>
+          <t>IC50 cell 3 (µM)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>IC50 mean (µM)</t>
+          <t>IC50 geomean (µM)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
@@ -839,7 +843,7 @@
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>n</t>
+          <t>n cells (finite)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
@@ -867,8 +871,10 @@
       <c r="F4" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="G4" s="2" t="n">
-        <v>2</v>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
     </row>
@@ -891,8 +897,10 @@
       <c r="F5" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>2</v>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
     </row>
@@ -915,8 +923,10 @@
       <c r="F6" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="G6" s="2" t="n">
-        <v>2</v>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
     </row>
@@ -939,8 +949,10 @@
       <c r="F7" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="G7" s="2" t="n">
-        <v>2</v>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H7" s="2" t="inlineStr"/>
     </row>
@@ -963,8 +975,10 @@
       <c r="F8" s="2" t="n">
         <v>88</v>
       </c>
-      <c r="G8" s="2" t="n">
-        <v>2</v>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
     </row>
@@ -987,8 +1001,10 @@
       <c r="F9" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="G9" s="2" t="n">
-        <v>2</v>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
     </row>
@@ -1011,8 +1027,10 @@
       <c r="F10" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="G10" s="2" t="n">
-        <v>2</v>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
     </row>
@@ -1035,8 +1053,10 @@
       <c r="F11" s="2" t="n">
         <v>64</v>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>2</v>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H11" s="2" t="inlineStr"/>
     </row>
@@ -1059,8 +1079,10 @@
       <c r="F12" s="2" t="n">
         <v>55</v>
       </c>
-      <c r="G12" s="2" t="n">
-        <v>2</v>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
     </row>
@@ -1083,8 +1105,10 @@
       <c r="F13" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="G13" s="2" t="n">
-        <v>2</v>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H13" s="2" t="inlineStr"/>
     </row>
@@ -1107,8 +1131,10 @@
       <c r="F14" s="2" t="n">
         <v>74</v>
       </c>
-      <c r="G14" s="2" t="n">
-        <v>2</v>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H14" s="2" t="inlineStr"/>
     </row>
@@ -1131,8 +1157,10 @@
       <c r="F15" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="G15" s="2" t="n">
-        <v>2</v>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H15" s="2" t="inlineStr"/>
     </row>
@@ -1155,8 +1183,10 @@
       <c r="F16" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="G16" s="2" t="n">
-        <v>2</v>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H16" s="2" t="inlineStr"/>
     </row>
@@ -1181,8 +1211,10 @@
       <c r="F17" s="2" t="n">
         <v>86</v>
       </c>
-      <c r="G17" s="2" t="n">
-        <v>3</v>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H17" s="2" t="inlineStr"/>
     </row>
@@ -1205,8 +1237,10 @@
       <c r="F18" s="2" t="n">
         <v>61</v>
       </c>
-      <c r="G18" s="2" t="n">
-        <v>2</v>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H18" s="2" t="inlineStr"/>
     </row>
@@ -1229,8 +1263,10 @@
       <c r="F19" s="2" t="n">
         <v>59</v>
       </c>
-      <c r="G19" s="2" t="n">
-        <v>2</v>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H19" s="2" t="inlineStr"/>
     </row>
@@ -1253,8 +1289,10 @@
       <c r="F20" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="G20" s="2" t="n">
-        <v>2</v>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H20" s="2" t="inlineStr"/>
     </row>
@@ -1277,8 +1315,10 @@
       <c r="F21" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="G21" s="2" t="n">
-        <v>2</v>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H21" s="2" t="inlineStr"/>
     </row>
@@ -1301,8 +1341,10 @@
       <c r="F22" s="2" t="n">
         <v>73</v>
       </c>
-      <c r="G22" s="2" t="n">
-        <v>2</v>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H22" s="2" t="inlineStr"/>
     </row>
@@ -1325,8 +1367,10 @@
       <c r="F23" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G23" s="2" t="n">
-        <v>2</v>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H23" s="2" t="inlineStr"/>
     </row>
@@ -1349,8 +1393,10 @@
       <c r="F24" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="G24" s="2" t="n">
-        <v>2</v>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H24" s="2" t="inlineStr"/>
     </row>
@@ -1373,8 +1419,10 @@
       <c r="F25" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="G25" s="2" t="n">
-        <v>2</v>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H25" s="2" t="inlineStr"/>
     </row>
@@ -1399,8 +1447,10 @@
       <c r="F26" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="G26" s="2" t="n">
-        <v>3</v>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
     </row>
@@ -1423,8 +1473,10 @@
       <c r="F27" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="G27" s="2" t="n">
-        <v>2</v>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H27" s="2" t="inlineStr"/>
     </row>
@@ -1447,8 +1499,10 @@
       <c r="F28" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="G28" s="2" t="n">
-        <v>2</v>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
     </row>
@@ -1471,8 +1525,10 @@
       <c r="F29" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="G29" s="2" t="n">
-        <v>2</v>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H29" s="2" t="inlineStr"/>
     </row>
@@ -1495,8 +1551,10 @@
       <c r="F30" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="G30" s="2" t="n">
-        <v>2</v>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H30" s="2" t="inlineStr"/>
     </row>
@@ -1519,8 +1577,10 @@
       <c r="F31" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="G31" s="2" t="n">
-        <v>2</v>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H31" s="2" t="inlineStr"/>
     </row>
@@ -1543,8 +1603,10 @@
       <c r="F32" s="2" t="n">
         <v>66</v>
       </c>
-      <c r="G32" s="2" t="n">
-        <v>2</v>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H32" s="2" t="inlineStr"/>
     </row>
@@ -1567,8 +1629,10 @@
       <c r="F33" s="2" t="n">
         <v>87</v>
       </c>
-      <c r="G33" s="2" t="n">
-        <v>2</v>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H33" s="2" t="inlineStr"/>
     </row>
@@ -1591,8 +1655,10 @@
       <c r="F34" s="2" t="n">
         <v>81</v>
       </c>
-      <c r="G34" s="2" t="n">
-        <v>2</v>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H34" s="2" t="inlineStr"/>
     </row>
@@ -1617,8 +1683,10 @@
       <c r="F35" s="2" t="n">
         <v>72</v>
       </c>
-      <c r="G35" s="2" t="n">
-        <v>3</v>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H35" s="2" t="inlineStr"/>
     </row>
@@ -1641,8 +1709,10 @@
       <c r="F36" s="2" t="n">
         <v>65</v>
       </c>
-      <c r="G36" s="2" t="n">
-        <v>2</v>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H36" s="2" t="inlineStr"/>
     </row>
@@ -1667,8 +1737,10 @@
       <c r="F37" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="G37" s="2" t="n">
-        <v>3</v>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H37" s="2" t="inlineStr"/>
     </row>
@@ -1691,8 +1763,10 @@
       <c r="F38" s="2" t="n">
         <v>85</v>
       </c>
-      <c r="G38" s="2" t="n">
-        <v>2</v>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H38" s="2" t="inlineStr"/>
     </row>
@@ -1717,8 +1791,10 @@
       <c r="F39" s="2" t="n">
         <v>82</v>
       </c>
-      <c r="G39" s="2" t="n">
-        <v>3</v>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>3 (3)</t>
+        </is>
       </c>
       <c r="H39" s="2" t="inlineStr"/>
     </row>
@@ -1741,8 +1817,10 @@
       <c r="F40" s="2" t="n">
         <v>50</v>
       </c>
-      <c r="G40" s="2" t="n">
-        <v>2</v>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
     </row>
@@ -1765,8 +1843,10 @@
       <c r="F41" s="2" t="n">
         <v>79</v>
       </c>
-      <c r="G41" s="2" t="n">
-        <v>2</v>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H41" s="2" t="inlineStr"/>
     </row>
@@ -1789,8 +1869,10 @@
       <c r="F42" s="2" t="n">
         <v>76</v>
       </c>
-      <c r="G42" s="2" t="n">
-        <v>2</v>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H42" s="2" t="inlineStr"/>
     </row>
@@ -1813,11 +1895,14 @@
       <c r="F43" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="G43" s="2" t="n">
-        <v>2</v>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>2 (2)</t>
+        </is>
       </c>
       <c r="H43" s="2" t="inlineStr"/>
     </row>
+    <row r="44"/>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
@@ -1825,8 +1910,16 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Compound IC50 = geometric mean of finite cell IC50s when they are the majority of accepted cells; otherwise reported as &gt;30 µM (or &gt;10 µM where solubility-limited)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -1836,15 +1929,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1865,10 +1961,20 @@
       </c>
       <c r="D1" s="6" t="inlineStr">
         <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E1" s="6" t="inlineStr">
+        <is>
+          <t>Historical mean</t>
+        </is>
+      </c>
+      <c r="F1" s="6" t="inlineStr">
+        <is>
           <t>Acceptance</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -1890,23 +1996,31 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>nM</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
           <t>5-50 nM</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>All runs met plate acceptance criteria. Checked by Ines Alvarado.</t>
+          <t>All accepted runs met plate acceptance criteria. Checked by Ines Alvarado.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>